--- a/scenarios/05_tom_optical_designer/5.1_wfe_budget_allocation/outputs/wfe_budget_results.xlsx
+++ b/scenarios/05_tom_optical_designer/5.1_wfe_budget_allocation/outputs/wfe_budget_results.xlsx
@@ -513,22 +513,22 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.4017</v>
+        <v>0.2418</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.6251</v>
+        <v>0.4609</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.8986</v>
+        <v>0.8861</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.7113</v>
+        <v>0.6021</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6.62</v>
+        <v>6.38</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>0</v>
@@ -545,22 +545,22 @@
         <v>0.9843</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.3955</v>
+        <v>0.238</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.4538</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>0.8846000000000001</v>
+        <v>0.8723</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.7004</v>
+        <v>0.593</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6.6</v>
+        <v>6.36</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>-0.02</v>
@@ -577,22 +577,22 @@
         <v>0.9388</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.3774</v>
+        <v>0.2271</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.5871</v>
+        <v>0.4329</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.844</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.6688</v>
+        <v>0.5663</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>6.53</v>
+        <v>6.29</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>-0.09</v>
@@ -609,22 +609,22 @@
         <v>0.8675</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.3491</v>
+        <v>0.2101</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.5427999999999999</v>
+        <v>0.4002</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.7804</v>
+        <v>0.7695</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.6194</v>
+        <v>0.5245</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>6.42</v>
+        <v>6.18</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>-0.2</v>
@@ -641,22 +641,22 @@
         <v>0.8195</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.3301</v>
+        <v>0.1986</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.513</v>
+        <v>0.3783</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.7376</v>
+        <v>0.7272</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.5861</v>
+        <v>0.4964</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>6.34</v>
+        <v>6.1</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>-0.28</v>
@@ -673,22 +673,22 @@
         <v>0.7766999999999999</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.3131</v>
+        <v>0.1884</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.4864</v>
+        <v>0.3587</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.6995</v>
+        <v>0.6896</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.5564</v>
+        <v>0.4713</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>6.27</v>
+        <v>6.03</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>-0.35</v>
@@ -705,22 +705,22 @@
         <v>0.6738</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.2723</v>
+        <v>0.1638</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.4225</v>
+        <v>0.3115</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.6077</v>
+        <v>0.599</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.485</v>
+        <v>0.411</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6.07</v>
+        <v>5.83</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>-0.55</v>
@@ -737,22 +737,22 @@
         <v>0.5664</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.2297</v>
+        <v>0.1382</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.3558</v>
+        <v>0.2623</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>0.5118</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.4104</v>
+        <v>0.348</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>5.83</v>
+        <v>5.59</v>
       </c>
       <c r="J9" s="2" t="n">
         <v>-0.79</v>
@@ -769,25 +769,25 @@
         <v>0.4613</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.1879</v>
+        <v>0.1131</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.2906</v>
+        <v>0.2142</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>0.418</v>
+        <v>0.4119</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.3374</v>
+        <v>0.2864</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5.55</v>
+        <v>5.31</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-1.08</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="11">
@@ -801,25 +801,25 @@
         <v>0.364</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.149</v>
+        <v>0.0897</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.2301</v>
+        <v>0.1696</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.3311</v>
+        <v>0.3262</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.2697</v>
+        <v>0.2292</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>5.22</v>
+        <v>4.99</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-1.4</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="12">
@@ -833,25 +833,25 @@
         <v>0.2783</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.1145</v>
+        <v>0.0689</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.1767</v>
+        <v>0.1302</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.2544</v>
+        <v>0.2505</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.21</v>
+        <v>0.1788</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>4.86</v>
+        <v>4.63</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>-1.76</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="13">
@@ -865,25 +865,25 @@
         <v>0.2062</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.0852</v>
+        <v>0.0513</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.1317</v>
+        <v>0.097</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>0.1896</v>
+        <v>0.1867</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.1596</v>
+        <v>0.1363</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>4.47</v>
+        <v>4.24</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-2.16</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="14">
@@ -897,25 +897,25 @@
         <v>0.0848</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.0351</v>
+        <v>0.0212</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.0554</v>
+        <v>0.0407</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.0788</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.074</v>
+        <v>0.0641</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>177.2</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3.36</v>
+        <v>3.15</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-3.26</v>
+        <v>-3.23</v>
       </c>
     </row>
   </sheetData>
